--- a/results/Hyderabad_state_summary_age_1901_oneshot.xlsx
+++ b/results/Hyderabad_state_summary_age_1901_oneshot.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Sections" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TABLE VII. AGE, SEX AND CIVIL C" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A—All Religions." sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -606,21 +606,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TABLE VII. AGE, SEX AND CIVIL CONDITION. A-All Religions.</t>
+          <t>TABLE VII. AGE, SEX AND CIVIL CONDITION. A—All Religions.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: TABLE VII. AGE, SEX AND CIVIL CONDITION. A-All Religions.</t>
+          <t>Source: TABLE VII. AGE, SEX AND CIVIL CONDITION. A—All Religions.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>TABLE VII. AGE, SEX AND CIVIL CONDITION. A-All Religions.</t>
+          <t>A—All Religions.</t>
         </is>
       </c>
     </row>
@@ -749,40 +749,40 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>23637951</v>
+        <v>11141142</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>12006115</v>
+        <v>5673629</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>11631836</v>
+        <v>5467513</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>9954931</v>
+        <v>4311525</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>5859653</v>
+        <v>2604439</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>4095278</v>
+        <v>1707086</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>11026878</v>
+        <v>5502367</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>5553295</v>
+        <v>2772795</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>5473583</v>
+        <v>2729572</v>
       </c>
       <c r="K6" s="17" t="n">
-        <v>2656142</v>
+        <v>1327250</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>593167</v>
+        <v>296395</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>2062975</v>
+        <v>1030855</v>
       </c>
       <c r="N6" s="18">
         <f>IF(B6=E6+H6+K6,"✓","✗")</f>
@@ -1924,14 +1924,14 @@
     <row r="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
-          <t>TABLE VII. AGE, SEX AND CIVIL CONDITION. A-All Religions.</t>
+          <t>TABLE VII. AGE, SEX AND CIVIL CONDITION. A—All Religions.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>TABLE VII. AGE, SEX AND CIVIL CONDITION. A-All Religions.</t>
+          <t>A—All Religions.</t>
         </is>
       </c>
     </row>
@@ -2060,40 +2060,40 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>23637951</v>
+        <v>11141142</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>12006115</v>
+        <v>5673629</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>11631836</v>
+        <v>5467513</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>9954931</v>
+        <v>4311525</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>5859653</v>
+        <v>2604439</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>4095278</v>
+        <v>1707086</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>11026878</v>
+        <v>5502367</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>5553295</v>
+        <v>2772795</v>
       </c>
       <c r="J5" s="17" t="n">
-        <v>5473583</v>
+        <v>2729572</v>
       </c>
       <c r="K5" s="17" t="n">
-        <v>2656142</v>
+        <v>1327250</v>
       </c>
       <c r="L5" s="17" t="n">
-        <v>593167</v>
+        <v>296395</v>
       </c>
       <c r="M5" s="17" t="n">
-        <v>2062975</v>
+        <v>1030855</v>
       </c>
       <c r="N5" s="18">
         <f>IF(B5=E5+H5+K5,"✓","✗")</f>
